--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,8 +152,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -596,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -621,7 +619,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-05 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +639,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.792</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -657,7 +655,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -688,7 +686,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.275</v>
+        <v>4.24</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +701,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.313</v>
+        <v>1.333</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,86 +725,71 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.792</v>
+        <v>0.798</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>comps_percentile</t>
+          <t>dcf_margin</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>dcf_margin</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Honest caveats (read before acting)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Honest caveats (read before acting)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -816,7 +799,6 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -825,6 +807,7 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -891,7 +874,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04532000064849853</v>
+        <v>0.0453600025177002</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1203,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839273.91812865</v>
+        <v>47839267.9245283</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1224,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.275</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="38">
@@ -1446,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1520,244 +1503,68 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>204512896</v>
+        <v>202838496</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>20.36</v>
+        <v>20.19</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BKTI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BK Technologies Corporation</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>306125632</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>22.83799</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>3.205</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CHOW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ChowChow Cloud International Ho</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>12687675</v>
-      </c>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="F7" s="34" t="n">
-        <v>-0.015</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D7" s="33">
+        <f>MEDIAN(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E7" s="33">
+        <f>MEDIAN(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F7" s="33">
+        <f>MEDIAN(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CNDT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Conduent Incorporated</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="n">
-        <v>242152672</v>
-      </c>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
-        <v>15.794</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>0.356</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D8" s="33">
+        <f>AVERAGE(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>AVERAGE(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F8" s="33">
+        <f>AVERAGE(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DMRC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Digimarc Corporation</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="n">
-        <v>298820960</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Target percentile vs peers</t>
+        </is>
       </c>
       <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
-        <v>-18.649</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>9.801</v>
-      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GPRO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GoPro, Inc.</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="n">
-        <v>158551840</v>
-      </c>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
-        <v>-2.586</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>0.355</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OCFT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OCFT</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PAYS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Paysign, Inc.</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="n">
-        <v>383513600</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <v>40.352943</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <v>18.439</v>
-      </c>
-      <c r="F12" s="34" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SDHI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Siddhi Acquisition Corp</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="n">
-        <v>363360352</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="34" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D15" s="35">
-        <f>MEDIAN(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E15" s="35">
-        <f>MEDIAN(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="35">
-        <f>MEDIAN(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D16" s="35">
-        <f>AVERAGE(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="35">
-        <f>AVERAGE(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="35">
-        <f>AVERAGE(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,6 +152,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -594,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -619,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -639,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -655,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -732,64 +734,79 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>dcf_margin</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -799,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -807,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0453600025177002</v>
+        <v>0.04535999774932861</v>
       </c>
     </row>
     <row r="6">
@@ -1429,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1515,56 +1532,232 @@
         <v>1.01</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BKTI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BK Technologies Corporation</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>299535840</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>22.346369</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>14.761</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>3.078</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHOW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ChowChow Cloud International Ho</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>12989340</v>
+      </c>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>-0.016</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CNDT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Conduent Incorporated</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>237298128</v>
+      </c>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
+        <v>15.475</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>0.349</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DMRC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Digimarc Corporation</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>303158144</v>
+      </c>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
+        <v>-17.599</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>9.249000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>155714688</v>
+      </c>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
+        <v>-2.384</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0.328</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OCFT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OCFT</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PAYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Paysign, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>379600192</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>39.941177</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>17.944</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SDHI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Siddhi Acquisition Corp</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>363360352</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="33">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="33">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="33">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="35">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="33">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="33">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="33">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="35">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n"/>
-      <c r="F9" s="34" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.793</v>
+        <v>0.796</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.890000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.24</v>
+        <v>4.1599</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.333</v>
+        <v>1.418</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.798</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04432000160217285</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839267.9245283</v>
+        <v>47839273.05944854</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.24</v>
+        <v>4.1599</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>202838496</v>
+        <v>199006592</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>20.19</v>
+        <v>19.81</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.38</v>
+        <v>10.13</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>299535840</v>
+        <v>302737152</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.346369</v>
+        <v>22.585197</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.761</v>
+        <v>14.838</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.078</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12989340</v>
+        <v>15392013</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.166</v>
+        <v>0.018</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.016</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>237298128</v>
+        <v>228767808</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.475</v>
+        <v>15.247</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>303158144</v>
+        <v>228185120</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-17.599</v>
+        <v>-13.477</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>9.249000000000001</v>
+        <v>7.083</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>155714688</v>
+        <v>145421360</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.384</v>
+        <v>-2.164</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.328</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>379600192</v>
+        <v>414541312</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>39.941177</v>
+        <v>43.617645</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>17.944</v>
+        <v>18.879</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>3.99</v>
+        <v>4.198</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>363360352</v>
+        <v>363011968</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>208.6</v>
+        <v>208.4</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.796</v>
+        <v>0.799</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.1599</v>
+        <v>4.07</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.418</v>
+        <v>1.469</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04432000160217285</v>
+        <v>0.04438000202178955</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839273.05944854</v>
+        <v>47839272.72727273</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.1599</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>199006592</v>
+        <v>194705840</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.81</v>
+        <v>19.38</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>10.13</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>302737152</v>
+        <v>308840160</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.585197</v>
+        <v>23.040503</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>14.838</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>15392013</v>
+        <v>15051309</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>228767808</v>
+        <v>224114912</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>228185120</v>
+        <v>209541808</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>145421360</v>
+        <v>138709088</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>414541312</v>
+        <v>407553088</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>43.617645</v>
+        <v>42.88235</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>18.879</v>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>10.05</v>
+        <v>9.93</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.07</v>
+        <v>3.995</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.469</v>
+        <v>1.486</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.828</v>
+        <v>0.841</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04438000202178955</v>
+        <v>0.04508999824523926</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.72727273</v>
+        <v>47839271.08886108</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.07</v>
+        <v>3.995</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>194705840</v>
+        <v>191117888</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.38</v>
+        <v>19.02</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.13</v>
+        <v>9.91</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>308840160</v>
+        <v>302400160</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.040503</v>
+        <v>22.560057</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.838</v>
+        <v>15.387</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.094</v>
+        <v>3.208</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>15051309</v>
+        <v>15264249</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.018</v>
+        <v>0.062</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>224114912</v>
+        <v>203952320</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.247</v>
+        <v>15.178</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>209541808</v>
+        <v>192126496</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-13.477</v>
+        <v>-12.283</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>7.083</v>
+        <v>6.455</v>
       </c>
     </row>
     <row r="10">
@@ -1634,11 +1634,11 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>138709088</v>
+        <v>129194240</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.164</v>
+        <v>-2.161</v>
       </c>
       <c r="F10" s="34" t="n">
         <v>0.297</v>
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>407553088</v>
+        <v>408950720</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>42.88235</v>
+        <v>43.02941</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>18.879</v>
+        <v>19.621</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.198</v>
+        <v>4.363</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>363011968</v>
+        <v>362663584</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>208.4</v>
+        <v>208.2</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.93</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.995</v>
+        <v>4.07</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.486</v>
+        <v>1.45</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.841</v>
+        <v>0.828</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04508999824523926</v>
+        <v>0.04484999656677246</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839271.08886108</v>
+        <v>47839272.72727273</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.995</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>191117888</v>
+        <v>194705840</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.02</v>
+        <v>19.38</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.91</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>0.96</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>302400160</v>
+        <v>303860384</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.560057</v>
+        <v>22.668995</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.387</v>
+        <v>14.997</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.208</v>
+        <v>3.127</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>15264249</v>
+        <v>14479920</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.006</v>
+        <v>-0.007</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>203952320</v>
+        <v>205503296</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.178</v>
+        <v>14.973</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>192126496</v>
+        <v>189558864</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-12.283</v>
+        <v>-11.049</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>6.455</v>
+        <v>5.807</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>129194240</v>
+        <v>128363848</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.161</v>
+        <v>-2.061</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.297</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>408950720</v>
+        <v>410348384</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>43.02941</v>
+        <v>43.17647</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.621</v>
+        <v>19.456</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.363</v>
+        <v>4.326</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>362663584</v>
+        <v>363011968</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>208.2</v>
+        <v>208.4</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.970000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.45</v>
+        <v>1.457</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.828</v>
+        <v>0.821</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04484999656677246</v>
+        <v>0.04409999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.72727273</v>
+        <v>47839272.01946472</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>194705840</v>
+        <v>196619408</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.38</v>
+        <v>19.57</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.880000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>303860384</v>
+        <v>319679616</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.668995</v>
+        <v>23.849161</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.997</v>
+        <v>15.775</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.127</v>
+        <v>3.289</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>14479920</v>
+        <v>13777219</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.007</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>205503296</v>
+        <v>200850368</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>14.973</v>
+        <v>14.905</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.338</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>189558864</v>
+        <v>180739584</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-11.049</v>
+        <v>-10.052</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>5.807</v>
+        <v>5.283</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>128363848</v>
+        <v>137082912</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.061</v>
+        <v>-2.11</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.283</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>410348384</v>
+        <v>456750176</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>43.17647</v>
+        <v>48.058823</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.456</v>
+        <v>22.149</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.326</v>
+        <v>4.925</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.11</v>
+        <v>4.205</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.457</v>
+        <v>1.378</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.821</v>
+        <v>0.804</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04409999847412109</v>
+        <v>0.04467000007629394</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.01946472</v>
+        <v>47839269.4411415</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.11</v>
+        <v>4.205</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>196619408</v>
+        <v>201164128</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.57</v>
+        <v>20.02</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.07</v>
+        <v>10.12</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>0.98</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>319679616</v>
+        <v>326381728</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.849161</v>
+        <v>24.349161</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.775</v>
+        <v>15.976</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.289</v>
+        <v>3.331</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13777219</v>
+        <v>14018550</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.12</v>
+        <v>0.138</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>200850368</v>
+        <v>239624576</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>14.905</v>
+        <v>15.315</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.336</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>180739584</v>
+        <v>195587248</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-10.052</v>
+        <v>-10.498</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>5.283</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>137082912</v>
+        <v>132533080</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.11</v>
+        <v>-2.137</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.29</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>456750176</v>
+        <v>475199072</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>48.058823</v>
+        <v>50</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>22.149</v>
+        <v>21.792</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.925</v>
+        <v>4.846</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.794</v>
+        <v>0.799</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.205</v>
+        <v>4.075</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.378</v>
+        <v>1.449</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.804</v>
+        <v>0.827</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04467000007629394</v>
+        <v>0.04480999946594239</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839269.4411415</v>
+        <v>47839269.69325154</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.205</v>
+        <v>4.075</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>201164128</v>
+        <v>194945024</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>20.02</v>
+        <v>19.4</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.12</v>
+        <v>10.28</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>326381728</v>
+        <v>322955776</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.349161</v>
+        <v>24.093575</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.976</v>
+        <v>16.352</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.331</v>
+        <v>3.409</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>14018550</v>
+        <v>13670748</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.138</v>
+        <v>0.129</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="8">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>239624576</v>
+        <v>230318768</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.315</v>
+        <v>15.338</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>0.346</v>
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>195587248</v>
+        <v>179511568</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-10.498</v>
+        <v>-10.616</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>5.517</v>
+        <v>5.579</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>132533080</v>
+        <v>125803488</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.137</v>
+        <v>-2.04</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.294</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>475199072</v>
+        <v>472403776</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50</v>
+        <v>49.70588</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>21.792</v>
+        <v>22.809</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.846</v>
+        <v>5.072</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.98</v>
+        <v>9.9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.075</v>
+        <v>4.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.449</v>
+        <v>1.409</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.827</v>
+        <v>0.821</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04480999946594239</v>
+        <v>0.044849997</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1.111</v>
+        <v>1.123</v>
       </c>
     </row>
     <row r="8">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839269.69325154</v>
+        <v>47839272.01946472</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.075</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>194945024</v>
+        <v>196619408</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.4</v>
+        <v>19.57</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.28</v>
+        <v>10.12</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>322955776</v>
+        <v>316946368</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.093575</v>
+        <v>23.645252</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>16.352</v>
+        <v>15.706</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.409</v>
+        <v>3.275</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13670748</v>
+        <v>13486200</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.129</v>
+        <v>0.145</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.012</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>230318768</v>
+        <v>234196192</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.338</v>
+        <v>15.429</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>179511568</v>
+        <v>174822832</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-10.616</v>
+        <v>-9.986000000000001</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>5.579</v>
+        <v>5.248</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>125803488</v>
+        <v>124557920</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.04</v>
+        <v>-2.02</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.28</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>472403776</v>
+        <v>461781696</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>49.70588</v>
+        <v>48.588238</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>22.809</v>
+        <v>21.985</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.072</v>
+        <v>4.889</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.044849997</v>
+        <v>0.04485000133514404</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.11</v>
+        <v>4.055</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.409</v>
+        <v>1.422</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.821</v>
+        <v>0.83</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04485000133514404</v>
+        <v>0.04532999992370605</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.01946472</v>
+        <v>47839270.03699137</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.11</v>
+        <v>4.055</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>196619408</v>
+        <v>193988240</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.57</v>
+        <v>19.31</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.12</v>
+        <v>9.99</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>316946368</v>
+        <v>312790304</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.645252</v>
+        <v>23.335196</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.706</v>
+        <v>15.07</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.275</v>
+        <v>3.142</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13486200</v>
+        <v>13507494</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.014</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>234196192</v>
+        <v>237499744</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.429</v>
+        <v>15.475</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>174822832</v>
+        <v>156064256</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-9.986000000000001</v>
+        <v>-9.002000000000001</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>5.248</v>
+        <v>4.731</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>124557920</v>
+        <v>131719992</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.02</v>
+        <v>-2.042</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.278</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>461781696</v>
+        <v>486939264</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>48.588238</v>
+        <v>51.235294</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>21.985</v>
+        <v>22.672</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.889</v>
+        <v>5.041</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>363011968</v>
+        <v>363708704</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>208.4</v>
+        <v>208.79999</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.799</v>
+        <v>0.804</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.055</v>
+        <v>3.91</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.422</v>
+        <v>1.496</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.83</v>
+        <v>0.856</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04532999992370605</v>
+        <v>0.04568999767303467</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839270.03699137</v>
+        <v>47839271.61125319</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.055</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>193988240</v>
+        <v>187051552</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.31</v>
+        <v>18.62</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.99</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>312790304</v>
+        <v>319267744</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.335196</v>
+        <v>23.818436</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.07</v>
+        <v>15.832</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.142</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13507494</v>
+        <v>13699140</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.115</v>
+        <v>0.136</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="8">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>237499744</v>
+        <v>235747152</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.475</v>
+        <v>15.452</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>0.349</v>
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>156064256</v>
+        <v>149230144</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-9.002000000000001</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.731</v>
+        <v>4.441</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>131719992</v>
+        <v>131962184</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.042</v>
+        <v>-2.107</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.281</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>486939264</v>
+        <v>506506304</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>51.235294</v>
+        <v>53.29412</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>22.672</v>
+        <v>24.183</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.041</v>
+        <v>5.378</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.804</v>
+        <v>0.796</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.76</v>
+        <v>9.69</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.91</v>
+        <v>4.135</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.496</v>
+        <v>1.343</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.856</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839271.61125319</v>
+        <v>47839276.42079807</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.91</v>
+        <v>4.135</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>187051552</v>
+        <v>197815408</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.62</v>
+        <v>19.69</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>9.710000000000001</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>319267744</v>
+        <v>314381568</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.818436</v>
+        <v>23.45391</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>15.832</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13699140</v>
+        <v>13209378</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>235747152</v>
+        <v>239624576</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>149230144</v>
+        <v>156064256</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>131962184</v>
+        <v>125872688</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>506506304</v>
+        <v>509301568</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>53.29412</v>
+        <v>53.588234</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>24.183</v>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.796</v>
+        <v>0.803</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.135</v>
+        <v>3.96</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.343</v>
+        <v>1.472</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04549000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839276.42079807</v>
+        <v>47839272.72727273</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.135</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>197815408</v>
+        <v>189443520</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.69</v>
+        <v>18.86</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.710000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>314381568</v>
+        <v>311479840</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.45391</v>
+        <v>23.23743</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.832</v>
+        <v>15.452</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.301</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>13209378</v>
+        <v>12943203</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.136</v>
+        <v>0.157</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.013</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>239624576</v>
+        <v>236522640</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.452</v>
+        <v>15.498</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>156064256</v>
+        <v>149678272</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.516</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.441</v>
+        <v>4.476</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>125872688</v>
+        <v>121063376</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.107</v>
+        <v>-1.975</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.289</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>509301568</v>
+        <v>483584896</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>53.588234</v>
+        <v>50.88235</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>24.183</v>
+        <v>23.194</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.378</v>
+        <v>5.158</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.803</v>
+        <v>0.798</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.789999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.472</v>
+        <v>1.378</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.847</v>
+        <v>0.823</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04549000263214111</v>
+        <v>0.04572999954223633</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.72727273</v>
+        <v>47839270.24390244</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>189443520</v>
+        <v>196141008</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.86</v>
+        <v>19.52</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.76</v>
+        <v>9.84</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>0.95</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>311479840</v>
+        <v>304964928</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.23743</v>
+        <v>22.751396</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.452</v>
+        <v>15.366</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.222</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12943203</v>
+        <v>12691224</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.015</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>236522640</v>
+        <v>248930400</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.498</v>
+        <v>15.452</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>149678272</v>
+        <v>137354464</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-8.516</v>
+        <v>-8.332000000000001</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.476</v>
+        <v>4.379</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>121063376</v>
+        <v>116721152</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.975</v>
+        <v>-1.991</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.271</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>483584896</v>
+        <v>489455040</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.88235</v>
+        <v>51.5</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>23.194</v>
+        <v>22.617</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.158</v>
+        <v>5.029</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.798</v>
+        <v>0.801</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.75</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.1</v>
+        <v>3.995</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.378</v>
+        <v>1.451</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.823</v>
+        <v>0.841</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04572999954223633</v>
+        <v>0.04550000190734863</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839270.24390244</v>
+        <v>47839271.08886108</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.1</v>
+        <v>3.995</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>196141008</v>
+        <v>191117888</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.52</v>
+        <v>19.02</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.84</v>
+        <v>10.1</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>304964928</v>
+        <v>311404928</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.751396</v>
+        <v>23.231844</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.366</v>
+        <v>14.497</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.204</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12691224</v>
+        <v>12425049</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.174</v>
+        <v>0.185</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.016</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>248930400</v>
+        <v>245052976</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.452</v>
+        <v>15.589</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>137354464</v>
+        <v>137580784</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-8.332000000000001</v>
+        <v>-7.715</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.379</v>
+        <v>4.055</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>116721152</v>
+        <v>118035920</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.991</v>
+        <v>-1.933</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.274</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>489455040</v>
+        <v>484272576</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>51.5</v>
+        <v>50.954704</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>22.617</v>
+        <v>23.276</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.029</v>
+        <v>5.176</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.995</v>
+        <v>3.99</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.451</v>
+        <v>1.456</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04550000190734863</v>
+        <v>0.04540999889373779</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839271.08886108</v>
+        <v>47839270.17543859</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.995</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>191117888</v>
+        <v>190878688</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.02</v>
+        <v>19</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.1</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>311404928</v>
+        <v>307136544</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.231844</v>
+        <v>22.913408</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.497</v>
+        <v>15.173</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.023</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12425049</v>
+        <v>12066600</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.185</v>
+        <v>0.205</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.017</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>245052976</v>
+        <v>251256848</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.589</v>
+        <v>15.68</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>137580784</v>
+        <v>134217496</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-7.715</v>
+        <v>-7.571</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.055</v>
+        <v>3.979</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118035920</v>
+        <v>114178096</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.933</v>
+        <v>-1.899</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.266</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>484272576</v>
+        <v>477994368</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.954704</v>
+        <v>50.294117</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>23.276</v>
+        <v>22.782</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.176</v>
+        <v>5.066</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.802</v>
+        <v>0.803</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.456</v>
+        <v>1.449</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.842</v>
+        <v>0.847</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04604000091552735</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839270.17543859</v>
+        <v>47839272.72727273</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>190878688</v>
+        <v>189443520</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19</v>
+        <v>18.86</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>9.880000000000001</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>307136544</v>
+        <v>302325280</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.913408</v>
+        <v>22.55447</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>15.173</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12066600</v>
+        <v>12311481</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>251256848</v>
+        <v>249705872</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>134217496</v>
+        <v>136010064</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>114178096</v>
+        <v>118814408</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>477994368</v>
+        <v>498925504</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.294117</v>
+        <v>52.49647</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>22.782</v>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.96</v>
+        <v>3.915</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.449</v>
+        <v>1.47</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.847</v>
+        <v>0.855</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04625999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.72727273</v>
+        <v>47839272.54150702</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.96</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>189443520</v>
+        <v>187290752</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.86</v>
+        <v>18.64</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.880000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>302325280</v>
+        <v>302025728</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.55447</v>
+        <v>22.532124</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.173</v>
+        <v>14.57</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.164</v>
+        <v>3.038</v>
       </c>
     </row>
     <row r="7">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12311481</v>
+        <v>12985791</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>249705872</v>
+        <v>241175536</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.68</v>
+        <v>15.635</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>136010064</v>
+        <v>134441568</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-7.571</v>
+        <v>-7.689</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>3.979</v>
+        <v>4.041</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118814408</v>
+        <v>123381528</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.899</v>
+        <v>-1.946</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.261</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>498925504</v>
+        <v>494648704</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>52.49647</v>
+        <v>52.04647</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>22.782</v>
+        <v>23.689</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.066</v>
+        <v>5.268</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.915</v>
+        <v>3.925</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.47</v>
+        <v>1.451</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.855</v>
+        <v>0.853</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04625999927520752</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839272.54150702</v>
+        <v>47839270.31847134</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.915</v>
+        <v>3.925</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>187290752</v>
+        <v>187769136</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.64</v>
+        <v>18.69</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.970000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>302025728</v>
+        <v>286877472</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.532124</v>
+        <v>21.402012</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.57</v>
+        <v>14.655</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.038</v>
+        <v>3.056</v>
       </c>
     </row>
     <row r="7">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12985791</v>
+        <v>12960948</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>-0.019</v>
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>241175536</v>
+        <v>233420704</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.635</v>
+        <v>15.521</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>134441568</v>
+        <v>140939584</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-7.689</v>
+        <v>-8.24</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.041</v>
+        <v>4.331</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>123381528</v>
+        <v>124644416</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.946</v>
+        <v>-2.02</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.267</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>494648704</v>
+        <v>500356640</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>52.04647</v>
+        <v>52.647057</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>23.689</v>
+        <v>23.964</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.268</v>
+        <v>5.329</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.804</v>
+        <v>0.801</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.925</v>
+        <v>4.02</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.451</v>
+        <v>1.396</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.853</v>
+        <v>0.837</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839270.31847134</v>
+        <v>47839271.64179105</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>3.925</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>187769136</v>
+        <v>192313872</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.69</v>
+        <v>19.14</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.880000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>286877472</v>
+        <v>298861888</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.402012</v>
+        <v>22.29609</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.655</v>
+        <v>14.336</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.056</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12960948</v>
+        <v>12563460</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.203</v>
+        <v>0.161</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.019</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>233420704</v>
+        <v>242726528</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.521</v>
+        <v>15.361</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>140939584</v>
+        <v>137802608</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-8.24</v>
+        <v>-7.519</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>4.331</v>
+        <v>3.951</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>124644416</v>
+        <v>118122424</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-2.02</v>
+        <v>-1.916</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.278</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>500356640</v>
+        <v>504829120</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>52.647057</v>
+        <v>53.117645</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>23.964</v>
+        <v>23.166</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.329</v>
+        <v>5.151</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>363708704</v>
+        <v>364405472</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>208.79999</v>
+        <v>209.2</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.801</v>
+        <v>0.702</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.630000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.02</v>
+        <v>5.19</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.396</v>
+        <v>0.802</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.837</v>
+        <v>0.71</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.583</v>
+        <v>0.4</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04783999919891357</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1.123</v>
+        <v>1.119</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>67782000</v>
+        <v>67502000</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>22689000</v>
+        <v>23681000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>47839271.64179105</v>
+        <v>48413465.89595375</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>4.02</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>192313872</v>
+        <v>251265888</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.14</v>
+        <v>21.62</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.619999999999999</v>
+        <v>11.81</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.93</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>298861888</v>
+        <v>275768512</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.29609</v>
+        <v>21.517647</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.336</v>
+        <v>13.312</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.989</v>
+        <v>2.727</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12563460</v>
+        <v>17070690</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>0.161</v>
+        <v>-0.007</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>-0.015</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>242726528</v>
+        <v>301710368</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>15.361</v>
+        <v>14.036</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.347</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>137802608</v>
+        <v>119343992</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-7.519</v>
+        <v>-4.756</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>3.951</v>
+        <v>3.647</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118122424</v>
+        <v>350805824</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-1.916</v>
+        <v>-3.463</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.263</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>504829120</v>
+        <v>759416000</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>53.117645</v>
+        <v>51.73077</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>23.166</v>
+        <v>27.216</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.151</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>364405472</v>
+        <v>366147392</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>209.2</v>
+        <v>26.275</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>
@@ -1749,11 +1749,9 @@
         </is>
       </c>
       <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n">
-        <v>0.333</v>
-      </c>
+      <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-07 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-07 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.702</v>
+        <v>0.746</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.802</v>
+        <v>0.838</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.71</v>
+        <v>0.732</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04835000038146973</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>48413465.89595375</v>
+        <v>48413465.34653465</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>251265888</v>
+        <v>244488000</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>21.62</v>
+        <v>21.04</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.81</v>
+        <v>11.62</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>275768512</v>
+        <v>276409312</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.517647</v>
+        <v>21.567648</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>13.312</v>
+        <v>13.156</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.727</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17070690</v>
+        <v>15977598</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>-0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>301710368</v>
+        <v>261274928</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>14.036</v>
+        <v>13.442</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.363</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>119343992</v>
+        <v>117096456</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-4.756</v>
+        <v>-4.728</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>3.647</v>
+        <v>3.626</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>350805824</v>
+        <v>287867136</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-3.463</v>
+        <v>-3.043</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.655</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>759416000</v>
+        <v>741348096</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>51.73077</v>
+        <v>50.500004</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>27.216</v>
+        <v>26.028</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>7.33</v>
+        <v>7.011</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>366147392</v>
+        <v>366844128</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>26.275</v>
+        <v>26.324999</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>
@@ -1751,7 +1751,7 @@
       <c r="D17" s="36" t="n"/>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/III_research.xlsx
+++ b/app/reports/III_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.746</v>
+        <v>0.779</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9.279999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.838</v>
+        <v>0.801</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.732</v>
+        <v>0.728</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04835000038146973</v>
+        <v>0.0492199993133545</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>48413465.34653465</v>
+        <v>48413464.56692913</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>244488000</v>
+        <v>245940400</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>21.04</v>
+        <v>21.17</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>276409312</v>
+        <v>272564512</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.567648</v>
+        <v>21.267645</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>13.156</v>
+        <v>13.253</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.695</v>
+        <v>2.715</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>15977598</v>
+        <v>15949206</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>-0.001</v>
+        <v>0.044</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="8">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>261274928</v>
+        <v>241057232</v>
       </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n">
-        <v>13.442</v>
+        <v>13.319</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.348</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="9">
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>117096456</v>
+        <v>111702376</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n">
-        <v>-4.728</v>
+        <v>-4.571</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>3.626</v>
+        <v>3.505</v>
       </c>
     </row>
     <row r="10">
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>287867136</v>
+        <v>303364512</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>-3.043</v>
+        <v>-2.974</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.576</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>741348096</v>
+        <v>745339968</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.500004</v>
+        <v>50.771923</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>26.028</v>
+        <v>26.341</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>7.011</v>
+        <v>7.095</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>366844128</v>
+        <v>367885792</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>26.324999</v>
+        <v>26.39975</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n"/>
@@ -1749,7 +1749,9 @@
         </is>
       </c>
       <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="E17" s="36" t="n">
+        <v>0.333</v>
+      </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>
       </c>
